--- a/AAII_Financials/Yearly/BOUYY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BOUYY_YR_FIN.xlsx
@@ -653,135 +653,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>58803200</v>
+      </c>
+      <c r="E8" s="3">
         <v>61960900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>47449000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>42811300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>42519900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>42655100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>40920500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>39713000</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>26137300</v>
+      </c>
+      <c r="E9" s="3">
         <v>28535400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>20638000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>19037900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>18831800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>19888900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>19030200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>18303300</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>32665900</v>
+      </c>
+      <c r="E10" s="3">
         <v>33425400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>26810900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>23773500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>23688100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>22766200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>21890300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>21409700</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -793,35 +805,39 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>78700</v>
+      </c>
+      <c r="E12" s="3">
         <v>78500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>67300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>46600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>75800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>70700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>84700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>86500</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -846,63 +862,72 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-145900</v>
+        <v>-71400</v>
       </c>
       <c r="E14" s="3">
+        <v>-166900</v>
+      </c>
+      <c r="F14" s="3">
         <v>-328100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-44400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>195700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-22400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-303400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-200500</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>3098700</v>
+      </c>
+      <c r="E15" s="3">
         <v>3207700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2857800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2749900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2680100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2415000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2309400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1916400</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -911,62 +936,69 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>59786700</v>
+        <v>56525500</v>
       </c>
       <c r="E17" s="3">
+        <v>59807700</v>
+      </c>
+      <c r="F17" s="3">
         <v>45776400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>40884800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>40949200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>40774300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>39129800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>38089600</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>2174200</v>
+        <v>2277700</v>
       </c>
       <c r="E18" s="3">
+        <v>2153200</v>
+      </c>
+      <c r="F18" s="3">
         <v>1672500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1926500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1570600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1880800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1790700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1623400</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -978,143 +1010,159 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-44200</v>
+        <v>109700</v>
       </c>
       <c r="E20" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="F20" s="3">
         <v>60900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-240000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-223900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-380400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-365200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-247400</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>5426100</v>
+        <v>5266600</v>
       </c>
       <c r="E21" s="3">
+        <v>5369700</v>
+      </c>
+      <c r="F21" s="3">
         <v>4469400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4916400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4474600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4676200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4465300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3787200</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>516600</v>
+      </c>
+      <c r="E22" s="3">
         <v>523900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>311000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>259300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>308300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>338900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>344600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>300200</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1903900</v>
+      </c>
+      <c r="E23" s="3">
         <v>1932100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1661900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1975400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1329700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1988600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2147900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1801200</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>638800</v>
+      </c>
+      <c r="E24" s="3">
         <v>604600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>453100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>491300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>387800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>507200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>487700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>359000</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1139,63 +1187,72 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1265100</v>
+      </c>
+      <c r="E26" s="3">
         <v>1327500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1208700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1484100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>941900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1481300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1660200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1442100</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1095300</v>
+      </c>
+      <c r="E27" s="3">
         <v>1149500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1039900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1279400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>851400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1328700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1497600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1299200</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1220,9 +1277,12 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1247,9 +1307,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1274,9 +1337,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1301,63 +1367,72 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>44200</v>
+        <v>-109700</v>
       </c>
       <c r="E32" s="3">
+        <v>8800</v>
+      </c>
+      <c r="F32" s="3">
         <v>-60900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>240000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>223900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>380400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>365200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>247400</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>1095400</v>
+      </c>
+      <c r="E33" s="3">
         <v>1149600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1039900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1279400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>851400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1328700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1497600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1299200</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1382,68 +1457,77 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>1095400</v>
+      </c>
+      <c r="E35" s="3">
         <v>1149600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1039900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1279400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>851400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1328700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1497600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1299200</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1455,8 +1539,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1468,35 +1553,39 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>5763500</v>
+      </c>
+      <c r="E41" s="3">
         <v>6132400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6130200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7393400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5167000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4010800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3352400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5787700</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -1521,198 +1610,222 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>20142900</v>
+      </c>
+      <c r="E43" s="3">
         <v>20987100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>21319900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>14347800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>13629400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12982800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12836000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12361900</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>2610000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2809800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2931500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2704400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2897900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3064800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3031800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2670500</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>2078000</v>
+        <v>940100</v>
       </c>
       <c r="E45" s="3">
+        <v>928500</v>
+      </c>
+      <c r="F45" s="3">
         <v>1233300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1005300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1145000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1483600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1859400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1318400</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>30751600</v>
+      </c>
+      <c r="E46" s="3">
         <v>32007300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>31614800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>26119600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>23395700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>21541900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21079700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>22496400</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>2000200</v>
+      </c>
+      <c r="E47" s="3">
         <v>2196300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1801900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1152100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2022000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1777600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3188700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3232500</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>12992000</v>
+      </c>
+      <c r="E48" s="3">
         <v>13485100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12460200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11132700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11197600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10393900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10172900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7994700</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>17689200</v>
+      </c>
+      <c r="E49" s="3">
         <v>17657800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17395500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11329500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11871600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9569100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9558000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8886900</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1737,9 +1850,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -1764,36 +1880,42 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>547700</v>
+      </c>
+      <c r="E52" s="3">
         <v>595800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>624100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>232000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>228700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>215500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>121400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>263000</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -1818,36 +1940,42 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>65311100</v>
+      </c>
+      <c r="E54" s="3">
         <v>67144900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>64759000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>50769900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>49678300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>44304800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>44867200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>43591500</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -1859,8 +1987,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -1872,170 +2001,189 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>11140900</v>
+      </c>
+      <c r="E57" s="3">
         <v>12165400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11879900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9400700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8807300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8297600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8499000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8992600</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>1884300</v>
+      </c>
+      <c r="E58" s="3">
         <v>1931000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2437700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2326900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1261200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2169200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2085000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1153900</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>15021200</v>
+      </c>
+      <c r="E59" s="3">
         <v>14084200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12747700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9864700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10062400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8045100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8304300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7669300</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>33288100</v>
+      </c>
+      <c r="E60" s="3">
         <v>33554800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>32019900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>25176800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>23711300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>21843800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>22224600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>21324400</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>13409300</v>
+      </c>
+      <c r="E61" s="3">
         <v>14477700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14634000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8277000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8462400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6382000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7297900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6953700</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>1837700</v>
+      </c>
+      <c r="E62" s="3">
         <v>1773000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1562500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1460300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1574300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1376900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1564000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1727900</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2060,9 +2208,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2087,9 +2238,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2114,36 +2268,42 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>50286800</v>
+      </c>
+      <c r="E66" s="3">
         <v>51546400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>49869600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>36225400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>35156000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>31062700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>32236100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>31084300</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2155,8 +2315,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2181,9 +2342,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2208,9 +2372,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2235,9 +2402,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2262,36 +2432,42 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>1095400</v>
+      </c>
+      <c r="E72" s="3">
         <v>1149600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1039900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1279400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>851400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1328700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1497600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1299200</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2316,9 +2492,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2343,9 +2522,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2370,36 +2552,42 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>13148400</v>
+      </c>
+      <c r="E76" s="3">
         <v>13715000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13051200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12673700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12722900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11676600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11045300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10852500</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2424,68 +2612,77 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>1095400</v>
+      </c>
+      <c r="E81" s="3">
         <v>1149600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1039900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1279400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>851400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1328700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1497600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1299200</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2497,35 +2694,39 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>2273500</v>
+      </c>
+      <c r="E83" s="3">
         <v>2378700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2014500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2018700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2093000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1878600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1841100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1384500</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2550,9 +2751,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2577,9 +2781,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -2604,9 +2811,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -2631,9 +2841,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -2658,36 +2871,42 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>5942300</v>
+        <v>5567900</v>
       </c>
       <c r="E89" s="3">
+        <v>5906900</v>
+      </c>
+      <c r="F89" s="3">
         <v>3182600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4066900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4166400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3785200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2957400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2472400</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -2699,35 +2918,39 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-2059200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2272600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2166300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2265400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2062400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1715900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2152500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1957300</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -2752,9 +2975,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -2779,36 +3005,42 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-3606000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2572100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9224100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1413600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1962100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-675600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3531000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1778300</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -2820,35 +3052,39 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>743300</v>
+      </c>
+      <c r="E96" s="3">
         <v>741700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>726700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>735800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>790200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>708100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>709900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>682000</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -2873,9 +3109,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -2900,9 +3139,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -2927,88 +3169,100 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-3760400</v>
+        <v>-2143100</v>
       </c>
       <c r="E100" s="3">
+        <v>-3725000</v>
+      </c>
+      <c r="F100" s="3">
         <v>5186500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-323000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1248900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2463200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1688800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-434700</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>89000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-64100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-34200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>72800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-119900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>98800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>61800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-224500</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-92100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-454300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-889200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2403000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>835500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>745100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2200600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>34800</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BOUYY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BOUYY_YR_FIN.xlsx
@@ -653,147 +653,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>58803200</v>
+        <v>66780600</v>
       </c>
       <c r="E8" s="3">
+        <v>58755600</v>
+      </c>
+      <c r="F8" s="3">
         <v>61960900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>47449000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>42811300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>42519900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>42655100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>40920500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>39713000</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>29179300</v>
+      </c>
+      <c r="E9" s="3">
         <v>26137300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>28535400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>20638000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>19037900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>18831800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>19888900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>19030200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18303300</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>32665900</v>
+        <v>37601300</v>
       </c>
       <c r="E10" s="3">
+        <v>32618300</v>
+      </c>
+      <c r="F10" s="3">
         <v>33425400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>26810900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>23773500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>23688100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>22766200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>21890300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>21409700</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -806,38 +818,42 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>82200</v>
+      </c>
+      <c r="E12" s="3">
         <v>78700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>78500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>67300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>46600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>75800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>70700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>84700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>86500</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -865,69 +881,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-71400</v>
+        <v>-90400</v>
       </c>
       <c r="E14" s="3">
+        <v>-39300</v>
+      </c>
+      <c r="F14" s="3">
         <v>-166900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-328100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-44400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>195700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-22400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-303400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-200500</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>3662100</v>
+      </c>
+      <c r="E15" s="3">
         <v>3098700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3207700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2857800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2749900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2680100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2415000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2309400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1916400</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -937,68 +962,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>56525500</v>
+        <v>64124700</v>
       </c>
       <c r="E17" s="3">
+        <v>56445800</v>
+      </c>
+      <c r="F17" s="3">
         <v>59807700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>45776400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>40884800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>40949200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>40774300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>39129800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>38089600</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>2277700</v>
+        <v>2655900</v>
       </c>
       <c r="E18" s="3">
+        <v>2309800</v>
+      </c>
+      <c r="F18" s="3">
         <v>2153200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1672500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1926500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1570600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1880800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1790700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1623400</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1011,158 +1043,174 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>109700</v>
+        <v>75100</v>
       </c>
       <c r="E20" s="3">
+        <v>130400</v>
+      </c>
+      <c r="F20" s="3">
         <v>-8800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>60900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-240000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-223900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-380400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-365200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-247400</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>5266600</v>
+        <v>6242800</v>
       </c>
       <c r="E21" s="3">
+        <v>5278000</v>
+      </c>
+      <c r="F21" s="3">
         <v>5369700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4469400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4916400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4474600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4676200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4465300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3787200</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>516600</v>
+        <v>562400</v>
       </c>
       <c r="E22" s="3">
+        <v>495900</v>
+      </c>
+      <c r="F22" s="3">
         <v>523900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>311000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>259300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>308300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>338900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>344600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>300200</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>2262500</v>
+      </c>
+      <c r="E23" s="3">
         <v>1903900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1932100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1661900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1975400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1329700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1988600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2147900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1801200</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>769100</v>
+      </c>
+      <c r="E24" s="3">
         <v>638800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>604600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>453100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>491300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>387800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>507200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>487700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>359000</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1190,69 +1238,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1493500</v>
+      </c>
+      <c r="E26" s="3">
         <v>1265100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1327500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1208700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1484100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>941900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1481300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1660200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1442100</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1336200</v>
+      </c>
+      <c r="E27" s="3">
         <v>1095300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1149500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1039900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1279400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>851400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1328700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1497600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1299200</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1280,9 +1337,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1310,9 +1370,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1340,9 +1403,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1370,69 +1436,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-109700</v>
+        <v>-75100</v>
       </c>
       <c r="E32" s="3">
+        <v>-130400</v>
+      </c>
+      <c r="F32" s="3">
         <v>8800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-60900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>240000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>223900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>380400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>365200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>247400</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>1336200</v>
+      </c>
+      <c r="E33" s="3">
         <v>1095400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1149600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1039900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1279400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>851400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1328700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1497600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1299200</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1460,74 +1535,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>1336200</v>
+      </c>
+      <c r="E35" s="3">
         <v>1095400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1149600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1039900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1279400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>851400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1328700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1497600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1299200</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1540,8 +1624,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1554,38 +1639,42 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>8847000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5763500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6132400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6130200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7393400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5167000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4010800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3352400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5787700</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -1613,219 +1702,243 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>22088800</v>
+      </c>
+      <c r="E43" s="3">
         <v>20142900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>20987100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>21319900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>14347800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>13629400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12982800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12836000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12361900</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>2693400</v>
+      </c>
+      <c r="E44" s="3">
         <v>2610000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2809800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2931500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2704400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2897900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3064800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3031800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2670500</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>940100</v>
+        <v>2686400</v>
       </c>
       <c r="E45" s="3">
+        <v>2235200</v>
+      </c>
+      <c r="F45" s="3">
         <v>928500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1233300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1005300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1145000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1483600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1859400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1318400</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>36315600</v>
+      </c>
+      <c r="E46" s="3">
         <v>30751600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>32007300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>31614800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>26119600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>23395700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21541900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21079700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>22496400</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>2198000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2000200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2196300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1801900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1152100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2022000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1777600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3188700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3232500</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>14890200</v>
+      </c>
+      <c r="E48" s="3">
         <v>12992000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13485100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12460200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11132700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>11197600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10393900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10172900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7994700</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>19761700</v>
+      </c>
+      <c r="E49" s="3">
         <v>17689200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17657800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17395500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11329500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11871600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9569100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9558000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8886900</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1853,9 +1966,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -1883,39 +1999,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>598800</v>
+      </c>
+      <c r="E52" s="3">
         <v>547700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>595800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>624100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>232000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>228700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>215500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>121400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>263000</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -1943,39 +2065,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>75283600</v>
+      </c>
+      <c r="E54" s="3">
         <v>65311100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>67144900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>64759000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>50769900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>49678300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>44304800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>44867200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>43591500</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -1988,8 +2116,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2002,188 +2131,207 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>11882100</v>
+      </c>
+      <c r="E57" s="3">
         <v>11140900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12165400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11879900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9400700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8807300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8297600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8499000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8992600</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>3106700</v>
+      </c>
+      <c r="E58" s="3">
         <v>1884300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1931000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2437700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2326900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1261200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2169200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2085000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1153900</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>15021200</v>
+        <v>23884000</v>
       </c>
       <c r="E59" s="3">
+        <v>20263000</v>
+      </c>
+      <c r="F59" s="3">
         <v>14084200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12747700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9864700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10062400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8045100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8304300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7669300</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>38872800</v>
+      </c>
+      <c r="E60" s="3">
         <v>33288100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>33554800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32019900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>25176800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>23711300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>21843800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>22224600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>21324400</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>14727000</v>
+      </c>
+      <c r="E61" s="3">
         <v>13409300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14477700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>14634000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8277000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8462400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6382000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7297900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6953700</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>2289500</v>
+      </c>
+      <c r="E62" s="3">
         <v>1837700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1773000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1562500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1460300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1574300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1376900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1564000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1727900</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2211,9 +2359,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2241,9 +2392,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2271,39 +2425,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>57846700</v>
+      </c>
+      <c r="E66" s="3">
         <v>50286800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>51546400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>49869600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>36225400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>35156000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>31062700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>32236100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>31084300</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2316,8 +2476,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2345,9 +2506,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2375,9 +2539,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2405,9 +2572,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2435,39 +2605,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>1336200</v>
+      </c>
+      <c r="E72" s="3">
         <v>1095400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1149600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1039900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1279400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>851400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1328700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1497600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1299200</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2495,9 +2671,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2525,9 +2704,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2555,39 +2737,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>15305900</v>
+      </c>
+      <c r="E76" s="3">
         <v>13148400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13715000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13051200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12673700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12722900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11676600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11045300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10852500</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2615,74 +2803,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>1336200</v>
+      </c>
+      <c r="E81" s="3">
         <v>1095400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1149600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1039900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1279400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>851400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1328700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1497600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1299200</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2695,38 +2892,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>2701700</v>
+      </c>
+      <c r="E83" s="3">
         <v>2273500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2378700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2014500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2018700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2093000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1878600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1841100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1384500</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2754,9 +2955,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2784,9 +2988,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -2814,9 +3021,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -2844,9 +3054,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -2874,39 +3087,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>6424800</v>
+      </c>
+      <c r="E89" s="3">
         <v>5567900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5906900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3182600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4066900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4166400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3785200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2957400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2472400</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -2919,38 +3138,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-2207400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2059200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2272600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2166300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2265400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2062400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1715900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2152500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1957300</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -2978,9 +3201,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3008,39 +3234,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-2329500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3606000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2572100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9224100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1413600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1962100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-675600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3531000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1778300</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3053,38 +3285,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>886500</v>
+      </c>
+      <c r="E96" s="3">
         <v>743300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>741700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>726700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>735800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>790200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>708100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>709900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>682000</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -3112,9 +3348,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -3142,9 +3381,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -3172,97 +3414,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-1947900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2143100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3725000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5186500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-323000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1248900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2463200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1688800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-434700</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-252400</v>
+      </c>
+      <c r="E101" s="3">
         <v>89000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-64100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-34200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>72800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-119900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>98800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>61800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-224500</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>1895000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-92100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-454300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-889200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2403000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>835500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>745100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2200600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>34800</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
